--- a/EJEMPLO_salida.xlsx
+++ b/EJEMPLO_salida.xlsx
@@ -681,51 +681,51 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>12:40:17</t>
+          <t>09:03:31</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>12:40:17.640</t>
+          <t>09:03:31.808</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:17.640-05:00</t>
+          <t>2026-10-14T09:03:31.808-05:00</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1790271617640</v>
+        <v>1791986611808</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>646</v>
+        <v>768</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>@dani_ar</t>
+          <t>@jorge_mx</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Daniela Arias</t>
+          <t>Jorge Ramírez</t>
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>7300000000004</v>
+        <v>7300000000007</v>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000004demo</t>
+          <t>MS4wLjABAAAA7300000000007demo</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>¿Vas a subir el resumen?</t>
+          <t>El audio se escucha perfecto</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>1677102779690366851</t>
+          <t>3974909215932584523</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr"/>
@@ -751,23 +751,23 @@
       <c r="U2" s="3" t="inlineStr"/>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>22</t>
         </is>
       </c>
       <c r="W2" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 38</t>
+          <t>Nivel de usuario 22</t>
         </is>
       </c>
       <c r="X2" s="4" t="inlineStr"/>
       <c r="Y2" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dani_ar</t>
+          <t>https://www.tiktok.com/@jorge_mx</t>
         </is>
       </c>
       <c r="Z2" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -777,51 +777,51 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>12:40:18</t>
+          <t>09:03:32</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>12:40:18.107</t>
+          <t>09:03:32.886</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:18.107-05:00</t>
+          <t>2026-10-14T09:03:32.886-05:00</t>
         </is>
       </c>
       <c r="F3" s="10" t="n">
-        <v>1790271618107</v>
+        <v>1791986612886</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>780</v>
+        <v>242</v>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>@nuria_bcn</t>
+          <t>@lucia.live</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>Núria Puig</t>
+          <t>Lucía Fernández</t>
         </is>
       </c>
       <c r="J3" s="10" t="n">
-        <v>7300000000008</v>
+        <v>7300000000003</v>
       </c>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000008demo</t>
+          <t>MS4wLjABAAAA7300000000003demo</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>Este tema me interesa mucho</t>
+          <t>Un saludo desde España 🇪🇸</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
-          <t>142716114279699688</t>
+          <t>1482543471363180485</t>
         </is>
       </c>
       <c r="O3" s="8" t="inlineStr"/>
@@ -842,28 +842,32 @@
         </is>
       </c>
       <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="8" t="inlineStr"/>
       <c r="V3" s="8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 26</t>
+          <t>Nivel de usuario 31, Amigo</t>
         </is>
       </c>
       <c r="X3" s="9" t="inlineStr"/>
       <c r="Y3" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nuria_bcn</t>
+          <t>https://www.tiktok.com/@lucia.live</t>
         </is>
       </c>
       <c r="Z3" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -873,51 +877,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>12:40:19</t>
+          <t>09:03:33</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>12:40:19.001</t>
+          <t>09:03:33.081</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:19.001-05:00</t>
+          <t>2026-10-14T09:03:33.081-05:00</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1790271619001</v>
+        <v>1791986613081</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>462</v>
+        <v>827</v>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>@topgifter99</t>
+          <t>@mod_sofia</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Carlos Núñez</t>
+          <t>Sofía Moderadora</t>
         </is>
       </c>
       <c r="J4" s="5" t="n">
-        <v>7300000000005</v>
+        <v>7300000000006</v>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000005demo</t>
+          <t>MS4wLjABAAAA7300000000006demo</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>Este tema me interesa mucho</t>
+          <t>¡Vamos con todo! 🚀</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -927,55 +931,43 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>2399852455303831072</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+          <t>4381606914186665036</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr"/>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W4" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 23, Suscriptor 18, Fan 27, Top gifter 30</t>
+          <t>Nivel de usuario 10, Moderador</t>
         </is>
       </c>
       <c r="X4" s="4" t="inlineStr"/>
       <c r="Y4" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@topgifter99</t>
+          <t>https://www.tiktok.com/@mod_sofia</t>
         </is>
       </c>
       <c r="Z4" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -985,51 +977,51 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>12:40:19</t>
+          <t>09:03:33</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>12:40:19.652</t>
+          <t>09:03:33.619</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:19.652-05:00</t>
+          <t>2026-10-14T09:03:33.619-05:00</t>
         </is>
       </c>
       <c r="F5" s="10" t="n">
-        <v>1790271619652</v>
+        <v>1791986613619</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>613</v>
+        <v>672</v>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>@nuria_bcn</t>
+          <t>@mod_sofia</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>Núria Puig</t>
+          <t>Sofía Moderadora</t>
         </is>
       </c>
       <c r="J5" s="10" t="n">
-        <v>7300000000008</v>
+        <v>7300000000006</v>
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000008demo</t>
+          <t>MS4wLjABAAAA7300000000006demo</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>No me pierdo ninguno 💪</t>
+          <t>Espectacular como siempre</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr">
@@ -1039,10 +1031,14 @@
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>3786782836827863357</t>
-        </is>
-      </c>
-      <c r="O5" s="8" t="inlineStr"/>
+          <t>1899082895856907954</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="P5" s="8" t="inlineStr"/>
       <c r="Q5" s="8" t="inlineStr">
         <is>
@@ -1055,23 +1051,23 @@
       <c r="U5" s="8" t="inlineStr"/>
       <c r="V5" s="8" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>18</t>
         </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 39</t>
+          <t>Nivel de usuario 18, Moderador</t>
         </is>
       </c>
       <c r="X5" s="9" t="inlineStr"/>
       <c r="Y5" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nuria_bcn</t>
+          <t>https://www.tiktok.com/@mod_sofia</t>
         </is>
       </c>
       <c r="Z5" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -1081,51 +1077,51 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>12:40:20</t>
+          <t>09:03:34</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>12:40:20.069</t>
+          <t>09:03:34.078</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:20.069-05:00</t>
+          <t>2026-10-14T09:03:34.078-05:00</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1790271620069</v>
+        <v>1791986614078</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>623</v>
+        <v>771</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>@ana_tt</t>
+          <t>@topgifter99</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Ana Torres</t>
+          <t>Carlos Núñez</t>
         </is>
       </c>
       <c r="J6" s="5" t="n">
-        <v>7300000000001</v>
+        <v>7300000000005</v>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000001demo</t>
+          <t>MS4wLjABAAAA7300000000005demo</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>¿Vas a subir el resumen?</t>
+          <t>Ya te seguí hace tiempo</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1135,7 +1131,7 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>3041888217859646964</t>
+          <t>1516101136687450179</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr"/>
@@ -1154,36 +1150,36 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 27, Suscriptor 9, Fan 16, Amigo</t>
+          <t>Nivel de usuario 1, Suscriptor 9, Fan 1, Top gifter 7</t>
         </is>
       </c>
       <c r="X6" s="4" t="inlineStr"/>
       <c r="Y6" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ana_tt</t>
+          <t>https://www.tiktok.com/@topgifter99</t>
         </is>
       </c>
       <c r="Z6" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -1193,29 +1189,29 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>12:40:20</t>
+          <t>09:03:35</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>12:40:20.895</t>
+          <t>09:03:35.223</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:20.895-05:00</t>
+          <t>2026-10-14T09:03:35.223-05:00</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1790271620895</v>
+        <v>1791986615223</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>330</v>
+        <v>251</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
@@ -1237,7 +1233,7 @@
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>Apoyando desde México 🇲🇽</t>
+          <t>¡Qué buen contenido! 🔥</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
@@ -1247,7 +1243,7 @@
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>3044343483701722422</t>
+          <t>4118790287775759617</t>
         </is>
       </c>
       <c r="O7" s="8" t="inlineStr"/>
@@ -1263,12 +1259,12 @@
       <c r="U7" s="8" t="inlineStr"/>
       <c r="V7" s="8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 24</t>
+          <t>Nivel de usuario 8</t>
         </is>
       </c>
       <c r="X7" s="9" t="inlineStr"/>
@@ -1279,7 +1275,7 @@
       </c>
       <c r="Z7" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -1289,51 +1285,51 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>12:40:21</t>
+          <t>09:03:35</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>12:40:21.007</t>
+          <t>09:03:35.413</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:21.007-05:00</t>
+          <t>2026-10-14T09:03:35.413-05:00</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1790271621007</v>
+        <v>1791986615413</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>489</v>
+        <v>646</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>@el_marce</t>
+          <t>@lucia.live</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Marcelo Ríos</t>
+          <t>Lucía Fernández</t>
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>7300000000002</v>
+        <v>7300000000003</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000002demo</t>
+          <t>MS4wLjABAAAA7300000000003demo</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Jajaja no puede ser 😂</t>
+          <t>Un saludo desde España 🇪🇸</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1343,7 +1339,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>3672648688249846369</t>
+          <t>4372369507586612909</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr"/>
@@ -1354,28 +1350,32 @@
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="inlineStr"/>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>39</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 17</t>
+          <t>Nivel de usuario 39, Amigo</t>
         </is>
       </c>
       <c r="X8" s="4" t="inlineStr"/>
       <c r="Y8" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@el_marce</t>
+          <t>https://www.tiktok.com/@lucia.live</t>
         </is>
       </c>
       <c r="Z8" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -1385,51 +1385,51 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>12:40:21</t>
+          <t>09:03:36</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>12:40:21.158</t>
+          <t>09:03:36.166</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:21.158-05:00</t>
+          <t>2026-10-14T09:03:36.166-05:00</t>
         </is>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1790271621158</v>
+        <v>1791986616166</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>813</v>
+        <v>150</v>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>@ana_tt</t>
+          <t>@lucia.live</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>Ana Torres</t>
+          <t>Lucía Fernández</t>
         </is>
       </c>
       <c r="J9" s="10" t="n">
-        <v>7300000000001</v>
+        <v>7300000000003</v>
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000001demo</t>
+          <t>MS4wLjABAAAA7300000000003demo</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>Espectacular como siempre</t>
+          <t>¿Cuál es tu opinión sobre eso?</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
@@ -1439,55 +1439,43 @@
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>2056127577055966391</t>
+          <t>2694703074979986072</t>
         </is>
       </c>
       <c r="O9" s="8" t="inlineStr"/>
-      <c r="P9" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="P9" s="8" t="inlineStr"/>
       <c r="Q9" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R9" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="R9" s="8" t="inlineStr"/>
       <c r="S9" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr"/>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+      <c r="U9" s="8" t="inlineStr"/>
       <c r="V9" s="8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 28, Suscriptor 17, Fan 22, Amigo</t>
+          <t>Nivel de usuario 2, Amigo</t>
         </is>
       </c>
       <c r="X9" s="9" t="inlineStr"/>
       <c r="Y9" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ana_tt</t>
+          <t>https://www.tiktok.com/@lucia.live</t>
         </is>
       </c>
       <c r="Z9" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -1497,51 +1485,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>12:40:21</t>
+          <t>09:03:36</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>12:40:21.988</t>
+          <t>09:03:36.193</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:21.988-05:00</t>
+          <t>2026-10-14T09:03:36.193-05:00</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1790271621988</v>
+        <v>1791986616193</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>582</v>
+        <v>787</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>@jorge_mx</t>
+          <t>@nuria_bcn</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Jorge Ramírez</t>
+          <t>Núria Puig</t>
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>7300000000007</v>
+        <v>7300000000008</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000007demo</t>
+          <t>MS4wLjABAAAA7300000000008demo</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>¿Haces sorteos?</t>
+          <t>¿Cuál es tu opinión sobre eso?</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1551,7 +1539,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>2717680697018900815</t>
+          <t>2674520709027755411</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr"/>
@@ -1567,23 +1555,23 @@
       <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 1</t>
+          <t>Nivel de usuario 4</t>
         </is>
       </c>
       <c r="X10" s="4" t="inlineStr"/>
       <c r="Y10" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jorge_mx</t>
+          <t>https://www.tiktok.com/@nuria_bcn</t>
         </is>
       </c>
       <c r="Z10" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -1593,51 +1581,51 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>12:40:22</t>
+          <t>09:03:37</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>12:40:22.618</t>
+          <t>09:03:37.110</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:22.618-05:00</t>
+          <t>2026-10-14T09:03:37.110-05:00</t>
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>1790271622618</v>
+        <v>1791986617110</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>@topgifter99</t>
+          <t>@el_marce</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>Carlos Núñez</t>
+          <t>Marcelo Ríos</t>
         </is>
       </c>
       <c r="J11" s="10" t="n">
-        <v>7300000000005</v>
+        <v>7300000000002</v>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000005demo</t>
+          <t>MS4wLjABAAAA7300000000002demo</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>Comparto el directo ahora mismo</t>
+          <t>Llegué tarde, ¿qué me perdí?</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -1647,55 +1635,39 @@
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>2856674587113439801</t>
+          <t>1503243586498339976</t>
         </is>
       </c>
       <c r="O11" s="8" t="inlineStr"/>
-      <c r="P11" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="P11" s="8" t="inlineStr"/>
       <c r="Q11" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="R11" s="8" t="inlineStr"/>
       <c r="S11" s="8" t="inlineStr"/>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="T11" s="8" t="inlineStr"/>
+      <c r="U11" s="8" t="inlineStr"/>
       <c r="V11" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 10, Suscriptor 7, Fan 28, Top gifter 39</t>
+          <t>Nivel de usuario 11</t>
         </is>
       </c>
       <c r="X11" s="9" t="inlineStr"/>
       <c r="Y11" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@topgifter99</t>
+          <t>https://www.tiktok.com/@el_marce</t>
         </is>
       </c>
       <c r="Z11" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -1705,51 +1677,51 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>12:40:23</t>
+          <t>09:03:36</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>12:40:23.115</t>
+          <t>09:03:36.993</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:23.115-05:00</t>
+          <t>2026-10-14T09:03:36.993-05:00</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1790271623115</v>
+        <v>1791986616993</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>600</v>
+        <v>807</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>@el_marce</t>
+          <t>@nuria_bcn</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Marcelo Ríos</t>
+          <t>Núria Puig</t>
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>7300000000002</v>
+        <v>7300000000008</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000002demo</t>
+          <t>MS4wLjABAAAA7300000000008demo</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Muy buena explicación, gracias</t>
+          <t>Jajaja no puede ser 😂</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1759,7 +1731,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>833485985185521783</t>
+          <t>2998612767382653521</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr"/>
@@ -1786,12 +1758,12 @@
       <c r="X12" s="4" t="inlineStr"/>
       <c r="Y12" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@el_marce</t>
+          <t>https://www.tiktok.com/@nuria_bcn</t>
         </is>
       </c>
       <c r="Z12" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -1801,51 +1773,51 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>12:40:23</t>
+          <t>09:03:37</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>12:40:23.937</t>
+          <t>09:03:37.858</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:23.937-05:00</t>
+          <t>2026-10-14T09:03:37.858-05:00</t>
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>1790271623937</v>
+        <v>1791986617858</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>320</v>
+        <v>566</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>@topgifter99</t>
+          <t>@lucia.live</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>Carlos Núñez</t>
+          <t>Lucía Fernández</t>
         </is>
       </c>
       <c r="J13" s="10" t="n">
-        <v>7300000000005</v>
+        <v>7300000000003</v>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000005demo</t>
+          <t>MS4wLjABAAAA7300000000003demo</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>Jajaja no puede ser 😂</t>
+          <t>Ya te seguí hace tiempo</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
@@ -1855,55 +1827,43 @@
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>3084115576310881084</t>
+          <t>3472244390248818162</t>
         </is>
       </c>
       <c r="O13" s="8" t="inlineStr"/>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="P13" s="8" t="inlineStr"/>
       <c r="Q13" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R13" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S13" s="8" t="inlineStr"/>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="R13" s="8" t="inlineStr"/>
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr"/>
+      <c r="U13" s="8" t="inlineStr"/>
       <c r="V13" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 5, Suscriptor 16, Fan 29, Top gifter 34</t>
+          <t>Nivel de usuario 1, Amigo</t>
         </is>
       </c>
       <c r="X13" s="9" t="inlineStr"/>
       <c r="Y13" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@topgifter99</t>
+          <t>https://www.tiktok.com/@lucia.live</t>
         </is>
       </c>
       <c r="Z13" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -1913,51 +1873,51 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>12:40:23</t>
+          <t>09:03:37</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>12:40:23.980</t>
+          <t>09:03:37.941</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:23.980-05:00</t>
+          <t>2026-10-14T09:03:37.941-05:00</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1790271623980</v>
+        <v>1791986617941</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>586</v>
+        <v>872</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>@nuria_bcn</t>
+          <t>@jorge_mx</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Núria Puig</t>
+          <t>Jorge Ramírez</t>
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>7300000000008</v>
+        <v>7300000000007</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000008demo</t>
+          <t>MS4wLjABAAAA7300000000007demo</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>Saludos desde Colombia 🇨🇴</t>
+          <t>Llegué tarde, ¿qué me perdí?</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1967,7 +1927,7 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>4118714885200180104</t>
+          <t>1274526321513580201</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr"/>
@@ -1983,23 +1943,23 @@
       <c r="U14" s="3" t="inlineStr"/>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 32</t>
+          <t>Nivel de usuario 35</t>
         </is>
       </c>
       <c r="X14" s="4" t="inlineStr"/>
       <c r="Y14" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nuria_bcn</t>
+          <t>https://www.tiktok.com/@jorge_mx</t>
         </is>
       </c>
       <c r="Z14" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -2009,51 +1969,51 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>12:40:24</t>
+          <t>09:03:38</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>12:40:24.414</t>
+          <t>09:03:38.825</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:24.414-05:00</t>
+          <t>2026-10-14T09:03:38.825-05:00</t>
         </is>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1790271624414</v>
+        <v>1791986618825</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>714</v>
+        <v>576</v>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>@ana_tt</t>
+          <t>@nuria_bcn</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>Ana Torres</t>
+          <t>Núria Puig</t>
         </is>
       </c>
       <c r="J15" s="10" t="n">
-        <v>7300000000001</v>
+        <v>7300000000008</v>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000001demo</t>
+          <t>MS4wLjABAAAA7300000000008demo</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>Primera vez por aquí, me quedo</t>
+          <t>Jajaja no puede ser 😂</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
@@ -2063,55 +2023,39 @@
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>2308342250305338354</t>
+          <t>1807447363994779566</t>
         </is>
       </c>
       <c r="O15" s="8" t="inlineStr"/>
-      <c r="P15" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="P15" s="8" t="inlineStr"/>
       <c r="Q15" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R15" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S15" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="R15" s="8" t="inlineStr"/>
+      <c r="S15" s="8" t="inlineStr"/>
       <c r="T15" s="8" t="inlineStr"/>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="U15" s="8" t="inlineStr"/>
       <c r="V15" s="8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>30</t>
         </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 16, Suscriptor 20, Fan 11, Amigo</t>
+          <t>Nivel de usuario 30</t>
         </is>
       </c>
       <c r="X15" s="9" t="inlineStr"/>
       <c r="Y15" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ana_tt</t>
+          <t>https://www.tiktok.com/@nuria_bcn</t>
         </is>
       </c>
       <c r="Z15" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -2121,51 +2065,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>12:40:24</t>
+          <t>09:03:39</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>12:40:24.862</t>
+          <t>09:03:39.345</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:24.862-05:00</t>
+          <t>2026-10-14T09:03:39.345-05:00</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>1790271624862</v>
+        <v>1791986619345</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>592</v>
+        <v>651</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>@ana_tt</t>
+          <t>@nuria_bcn</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Ana Torres</t>
+          <t>Núria Puig</t>
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>7300000000001</v>
+        <v>7300000000008</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000001demo</t>
+          <t>MS4wLjABAAAA7300000000008demo</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>Espectacular como siempre</t>
+          <t>Llegué tarde, ¿qué me perdí?</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -2175,55 +2119,39 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>373306151772436808</t>
+          <t>1728416160472647402</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr"/>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="P16" s="3" t="inlineStr"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
       <c r="T16" s="3" t="inlineStr"/>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="U16" s="3" t="inlineStr"/>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 40, Suscriptor 12, Fan 3, Amigo</t>
+          <t>Nivel de usuario 15</t>
         </is>
       </c>
       <c r="X16" s="4" t="inlineStr"/>
       <c r="Y16" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ana_tt</t>
+          <t>https://www.tiktok.com/@nuria_bcn</t>
         </is>
       </c>
       <c r="Z16" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -2233,51 +2161,51 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>12:40:25</t>
+          <t>09:03:39</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>12:40:25.725</t>
+          <t>09:03:39.756</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:25.725-05:00</t>
+          <t>2026-10-14T09:03:39.756-05:00</t>
         </is>
       </c>
       <c r="F17" s="10" t="n">
-        <v>1790271625725</v>
+        <v>1791986619756</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>260</v>
+        <v>670</v>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>@nuria_bcn</t>
+          <t>@dani_ar</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>Núria Puig</t>
+          <t>Daniela Arias</t>
         </is>
       </c>
       <c r="J17" s="10" t="n">
-        <v>7300000000008</v>
+        <v>7300000000004</v>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000008demo</t>
+          <t>MS4wLjABAAAA7300000000004demo</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>No me pierdo ninguno 💪</t>
+          <t>Saludos desde Colombia 🇨🇴</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
@@ -2287,7 +2215,7 @@
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>1734969350756147734</t>
+          <t>2072944326436055376</t>
         </is>
       </c>
       <c r="O17" s="8" t="inlineStr"/>
@@ -2303,23 +2231,23 @@
       <c r="U17" s="8" t="inlineStr"/>
       <c r="V17" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 15</t>
+          <t>Nivel de usuario 10</t>
         </is>
       </c>
       <c r="X17" s="9" t="inlineStr"/>
       <c r="Y17" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nuria_bcn</t>
+          <t>https://www.tiktok.com/@dani_ar</t>
         </is>
       </c>
       <c r="Z17" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -2329,51 +2257,51 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>12:40:26</t>
+          <t>09:03:40</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>12:40:26.437</t>
+          <t>09:03:40.172</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:26.437-05:00</t>
+          <t>2026-10-14T09:03:40.172-05:00</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>1790271626437</v>
+        <v>1791986620172</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>425</v>
+        <v>730</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>@lucia.live</t>
+          <t>@nuria_bcn</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Lucía Fernández</t>
+          <t>Núria Puig</t>
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>7300000000003</v>
+        <v>7300000000008</v>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000003demo</t>
+          <t>MS4wLjABAAAA7300000000008demo</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>Primera vez por aquí, me quedo</t>
+          <t>¡Hola a todos! 👋</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2383,7 +2311,7 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>2264334564012172733</t>
+          <t>481810598944559779</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr"/>
@@ -2394,32 +2322,28 @@
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="S18" s="3" t="inlineStr"/>
       <c r="T18" s="3" t="inlineStr"/>
       <c r="U18" s="3" t="inlineStr"/>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 24, Amigo</t>
+          <t>Nivel de usuario 36</t>
         </is>
       </c>
       <c r="X18" s="4" t="inlineStr"/>
       <c r="Y18" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lucia.live</t>
+          <t>https://www.tiktok.com/@nuria_bcn</t>
         </is>
       </c>
       <c r="Z18" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -2429,51 +2353,51 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>12:40:26</t>
+          <t>09:03:40</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>12:40:26.951</t>
+          <t>09:03:40.623</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:26.951-05:00</t>
+          <t>2026-10-14T09:03:40.623-05:00</t>
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>1790271626951</v>
+        <v>1791986620623</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>482</v>
+        <v>862</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>@ana_tt</t>
+          <t>@lucia.live</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>Ana Torres</t>
+          <t>Lucía Fernández</t>
         </is>
       </c>
       <c r="J19" s="10" t="n">
-        <v>7300000000001</v>
+        <v>7300000000003</v>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000001demo</t>
+          <t>MS4wLjABAAAA7300000000003demo</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>Apoyando desde México 🇲🇽</t>
+          <t>Espectacular como siempre</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
@@ -2483,55 +2407,43 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>2991711852337064437</t>
+          <t>2322120344764083116</t>
         </is>
       </c>
       <c r="O19" s="8" t="inlineStr"/>
-      <c r="P19" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="P19" s="8" t="inlineStr"/>
       <c r="Q19" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R19" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="R19" s="8" t="inlineStr"/>
       <c r="S19" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr"/>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+      <c r="U19" s="8" t="inlineStr"/>
       <c r="V19" s="8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 18, Suscriptor 20, Fan 23, Amigo</t>
+          <t>Nivel de usuario 26, Amigo</t>
         </is>
       </c>
       <c r="X19" s="9" t="inlineStr"/>
       <c r="Y19" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ana_tt</t>
+          <t>https://www.tiktok.com/@lucia.live</t>
         </is>
       </c>
       <c r="Z19" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -2541,51 +2453,51 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>12:40:27</t>
+          <t>09:03:41</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>12:40:27.752</t>
+          <t>09:03:41.497</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:27.752-05:00</t>
+          <t>2026-10-14T09:03:41.497-05:00</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>1790271627752</v>
+        <v>1791986621497</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>455</v>
+        <v>392</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>@lucia.live</t>
+          <t>@dani_ar</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Lucía Fernández</t>
+          <t>Daniela Arias</t>
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>7300000000003</v>
+        <v>7300000000004</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000003demo</t>
+          <t>MS4wLjABAAAA7300000000004demo</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>Saludos desde Argentina 🇦🇷</t>
+          <t>¡Vamos con todo! 🚀</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -2595,7 +2507,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>912389048031074029</t>
+          <t>1854073416206661421</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr"/>
@@ -2606,32 +2518,28 @@
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="S20" s="3" t="inlineStr"/>
       <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="inlineStr"/>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>39</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 3, Amigo</t>
+          <t>Nivel de usuario 39</t>
         </is>
       </c>
       <c r="X20" s="4" t="inlineStr"/>
       <c r="Y20" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lucia.live</t>
+          <t>https://www.tiktok.com/@dani_ar</t>
         </is>
       </c>
       <c r="Z20" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -2641,51 +2549,51 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>12:40:27</t>
+          <t>09:03:41</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>12:40:27.685</t>
+          <t>09:03:41.932</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:27.685-05:00</t>
+          <t>2026-10-14T09:03:41.932-05:00</t>
         </is>
       </c>
       <c r="F21" s="10" t="n">
-        <v>1790271627685</v>
+        <v>1791986621932</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>860</v>
+        <v>699</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>@nuria_bcn</t>
+          <t>@topgifter99</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>Núria Puig</t>
+          <t>Carlos Núñez</t>
         </is>
       </c>
       <c r="J21" s="10" t="n">
-        <v>7300000000008</v>
+        <v>7300000000005</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000008demo</t>
+          <t>MS4wLjABAAAA7300000000005demo</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>¡Vamos con todo! 🚀</t>
+          <t>Este tema me interesa mucho</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
@@ -2695,39 +2603,55 @@
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>2058014289599023904</t>
+          <t>1093288244650032041</t>
         </is>
       </c>
       <c r="O21" s="8" t="inlineStr"/>
-      <c r="P21" s="8" t="inlineStr"/>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q21" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R21" s="8" t="inlineStr"/>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="S21" s="8" t="inlineStr"/>
-      <c r="T21" s="8" t="inlineStr"/>
-      <c r="U21" s="8" t="inlineStr"/>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="V21" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 6</t>
+          <t>Nivel de usuario 8, Suscriptor 19, Fan 17, Top gifter 11</t>
         </is>
       </c>
       <c r="X21" s="9" t="inlineStr"/>
       <c r="Y21" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nuria_bcn</t>
+          <t>https://www.tiktok.com/@topgifter99</t>
         </is>
       </c>
       <c r="Z21" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -2737,51 +2661,51 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>12:40:28</t>
+          <t>09:03:42</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>12:40:28.275</t>
+          <t>09:03:42.975</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:28.275-05:00</t>
+          <t>2026-10-14T09:03:42.975-05:00</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1790271628275</v>
+        <v>1791986622975</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>797</v>
+        <v>325</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>@mod_sofia</t>
+          <t>@nuria_bcn</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Sofía Moderadora</t>
+          <t>Núria Puig</t>
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>7300000000006</v>
+        <v>7300000000008</v>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000006demo</t>
+          <t>MS4wLjABAAAA7300000000008demo</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>¿Puedes repetir eso?</t>
+          <t>Muy buena explicación, gracias</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2791,14 +2715,10 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>2230761066329219984</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+          <t>555667239144390896</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="inlineStr"/>
       <c r="Q22" s="3" t="inlineStr">
         <is>
@@ -2811,23 +2731,23 @@
       <c r="U22" s="3" t="inlineStr"/>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 32, Moderador</t>
+          <t>Nivel de usuario 12</t>
         </is>
       </c>
       <c r="X22" s="4" t="inlineStr"/>
       <c r="Y22" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mod_sofia</t>
+          <t>https://www.tiktok.com/@nuria_bcn</t>
         </is>
       </c>
       <c r="Z22" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -2837,51 +2757,51 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>12:40:29</t>
+          <t>09:03:43</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>12:40:29.117</t>
+          <t>09:03:43.750</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:29.117-05:00</t>
+          <t>2026-10-14T09:03:43.750-05:00</t>
         </is>
       </c>
       <c r="F23" s="10" t="n">
-        <v>1790271629117</v>
+        <v>1791986623750</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>374</v>
+        <v>266</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>@topgifter99</t>
+          <t>@mod_sofia</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>Carlos Núñez</t>
+          <t>Sofía Moderadora</t>
         </is>
       </c>
       <c r="J23" s="10" t="n">
-        <v>7300000000005</v>
+        <v>7300000000006</v>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000005demo</t>
+          <t>MS4wLjABAAAA7300000000006demo</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>¡Qué buen contenido! 🔥</t>
+          <t>Saludos desde Colombia 🇨🇴</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
@@ -2891,55 +2811,43 @@
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>382034730839989375</t>
-        </is>
-      </c>
-      <c r="O23" s="8" t="inlineStr"/>
-      <c r="P23" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+          <t>3048547062385642848</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr"/>
       <c r="Q23" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R23" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="R23" s="8" t="inlineStr"/>
       <c r="S23" s="8" t="inlineStr"/>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="T23" s="8" t="inlineStr"/>
+      <c r="U23" s="8" t="inlineStr"/>
       <c r="V23" s="8" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>18</t>
         </is>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 38, Suscriptor 19, Fan 20, Top gifter 28</t>
+          <t>Nivel de usuario 18, Moderador</t>
         </is>
       </c>
       <c r="X23" s="9" t="inlineStr"/>
       <c r="Y23" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@topgifter99</t>
+          <t>https://www.tiktok.com/@mod_sofia</t>
         </is>
       </c>
       <c r="Z23" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -2949,51 +2857,51 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>12:40:29</t>
+          <t>09:03:44</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>12:40:29.626</t>
+          <t>09:03:44.379</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:29.626-05:00</t>
+          <t>2026-10-14T09:03:44.379-05:00</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>1790271629626</v>
+        <v>1791986624379</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>400</v>
+        <v>146</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>@el_marce</t>
+          <t>@jorge_mx</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Marcelo Ríos</t>
+          <t>Jorge Ramírez</t>
         </is>
       </c>
       <c r="J24" s="5" t="n">
-        <v>7300000000002</v>
+        <v>7300000000007</v>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000002demo</t>
+          <t>MS4wLjABAAAA7300000000007demo</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>¡Hola a todos! 👋</t>
+          <t>¿Cuál es tu opinión sobre eso?</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -3003,7 +2911,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>2327763286419395692</t>
+          <t>2823424256775560069</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr"/>
@@ -3019,23 +2927,23 @@
       <c r="U24" s="3" t="inlineStr"/>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>33</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 11</t>
+          <t>Nivel de usuario 33</t>
         </is>
       </c>
       <c r="X24" s="4" t="inlineStr"/>
       <c r="Y24" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@el_marce</t>
+          <t>https://www.tiktok.com/@jorge_mx</t>
         </is>
       </c>
       <c r="Z24" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -3045,51 +2953,51 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>12:40:30</t>
+          <t>09:03:44</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>12:40:30.567</t>
+          <t>09:03:44.756</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:30.567-05:00</t>
+          <t>2026-10-14T09:03:44.756-05:00</t>
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1790271630567</v>
+        <v>1791986624756</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>@el_marce</t>
+          <t>@nuria_bcn</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>Marcelo Ríos</t>
+          <t>Núria Puig</t>
         </is>
       </c>
       <c r="J25" s="10" t="n">
-        <v>7300000000002</v>
+        <v>7300000000008</v>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000002demo</t>
+          <t>MS4wLjABAAAA7300000000008demo</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>Espectacular como siempre</t>
+          <t>¿De qué trata el directo hoy?</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
@@ -3099,7 +3007,7 @@
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>1876800501052609926</t>
+          <t>1579437151154487900</t>
         </is>
       </c>
       <c r="O25" s="8" t="inlineStr"/>
@@ -3115,23 +3023,23 @@
       <c r="U25" s="8" t="inlineStr"/>
       <c r="V25" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 15</t>
+          <t>Nivel de usuario 24</t>
         </is>
       </c>
       <c r="X25" s="9" t="inlineStr"/>
       <c r="Y25" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@el_marce</t>
+          <t>https://www.tiktok.com/@nuria_bcn</t>
         </is>
       </c>
       <c r="Z25" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -3141,29 +3049,29 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>12:40:30</t>
+          <t>09:03:45</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>12:40:30.338</t>
+          <t>09:03:45.323</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:30.338-05:00</t>
+          <t>2026-10-14T09:03:45.323-05:00</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>1790271630338</v>
+        <v>1791986625323</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>817</v>
+        <v>231</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
@@ -3185,7 +3093,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>Esto es oro puro</t>
+          <t>Llegué tarde, ¿qué me perdí?</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -3195,7 +3103,7 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>1983012880616526834</t>
+          <t>4363022978725637340</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr"/>
@@ -3222,17 +3130,17 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 2, Suscriptor 8, Fan 18, Top gifter 1</t>
+          <t>Nivel de usuario 8, Suscriptor 15, Fan 9, Top gifter 13</t>
         </is>
       </c>
       <c r="X26" s="4" t="inlineStr"/>
@@ -3243,7 +3151,7 @@
       </c>
       <c r="Z26" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -3253,51 +3161,51 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>12:40:31</t>
+          <t>09:03:45</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>12:40:31.487</t>
+          <t>09:03:45.271</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:31.487-05:00</t>
+          <t>2026-10-14T09:03:45.271-05:00</t>
         </is>
       </c>
       <c r="F27" s="10" t="n">
-        <v>1790271631487</v>
+        <v>1791986625271</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>207</v>
+        <v>747</v>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>@lucia.live</t>
+          <t>@jorge_mx</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>Lucía Fernández</t>
+          <t>Jorge Ramírez</t>
         </is>
       </c>
       <c r="J27" s="10" t="n">
-        <v>7300000000003</v>
+        <v>7300000000007</v>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000003demo</t>
+          <t>MS4wLjABAAAA7300000000007demo</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>Jajaja no puede ser 😂</t>
+          <t>Apoyando desde México 🇲🇽</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
@@ -3307,7 +3215,7 @@
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>2323039736270873803</t>
+          <t>2606923664483920136</t>
         </is>
       </c>
       <c r="O27" s="8" t="inlineStr"/>
@@ -3318,32 +3226,28 @@
         </is>
       </c>
       <c r="R27" s="8" t="inlineStr"/>
-      <c r="S27" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="S27" s="8" t="inlineStr"/>
       <c r="T27" s="8" t="inlineStr"/>
       <c r="U27" s="8" t="inlineStr"/>
       <c r="V27" s="8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 24, Amigo</t>
+          <t>Nivel de usuario 28</t>
         </is>
       </c>
       <c r="X27" s="9" t="inlineStr"/>
       <c r="Y27" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lucia.live</t>
+          <t>https://www.tiktok.com/@jorge_mx</t>
         </is>
       </c>
       <c r="Z27" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -3353,51 +3257,51 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>12:40:31</t>
+          <t>09:03:46</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>12:40:31.920</t>
+          <t>09:03:46.008</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:31.920-05:00</t>
+          <t>2026-10-14T09:03:46.008-05:00</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>1790271631920</v>
+        <v>1791986626008</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>298</v>
+        <v>516</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>@dani_ar</t>
+          <t>@el_marce</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Daniela Arias</t>
+          <t>Marcelo Ríos</t>
         </is>
       </c>
       <c r="J28" s="5" t="n">
-        <v>7300000000004</v>
+        <v>7300000000002</v>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000004demo</t>
+          <t>MS4wLjABAAAA7300000000002demo</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>¿Se puede participar?</t>
+          <t>¿Cuál es tu opinión sobre eso?</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -3407,7 +3311,7 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>502924586822379166</t>
+          <t>1880894015402336496</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr"/>
@@ -3423,23 +3327,23 @@
       <c r="U28" s="3" t="inlineStr"/>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>27</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 36</t>
+          <t>Nivel de usuario 27</t>
         </is>
       </c>
       <c r="X28" s="4" t="inlineStr"/>
       <c r="Y28" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dani_ar</t>
+          <t>https://www.tiktok.com/@el_marce</t>
         </is>
       </c>
       <c r="Z28" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -3449,51 +3353,51 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>12:40:31</t>
+          <t>09:03:46</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>12:40:31.827</t>
+          <t>09:03:46.830</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:31.827-05:00</t>
+          <t>2026-10-14T09:03:46.830-05:00</t>
         </is>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1790271631827</v>
+        <v>1791986626830</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>727</v>
+        <v>202</v>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>@mod_sofia</t>
+          <t>@topgifter99</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>Sofía Moderadora</t>
+          <t>Carlos Núñez</t>
         </is>
       </c>
       <c r="J29" s="10" t="n">
-        <v>7300000000006</v>
+        <v>7300000000005</v>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000006demo</t>
+          <t>MS4wLjABAAAA7300000000005demo</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>Un saludo desde España 🇪🇸</t>
+          <t>Este tema me interesa mucho</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
@@ -3503,43 +3407,55 @@
       </c>
       <c r="N29" s="9" t="inlineStr">
         <is>
-          <t>4205510365291415918</t>
-        </is>
-      </c>
-      <c r="O29" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="P29" s="8" t="inlineStr"/>
+          <t>2652630551994112946</t>
+        </is>
+      </c>
+      <c r="O29" s="8" t="inlineStr"/>
+      <c r="P29" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q29" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R29" s="8" t="inlineStr"/>
+      <c r="R29" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="S29" s="8" t="inlineStr"/>
-      <c r="T29" s="8" t="inlineStr"/>
-      <c r="U29" s="8" t="inlineStr"/>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="V29" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 15, Moderador</t>
+          <t>Nivel de usuario 8, Suscriptor 9, Fan 5, Top gifter 43</t>
         </is>
       </c>
       <c r="X29" s="9" t="inlineStr"/>
       <c r="Y29" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mod_sofia</t>
+          <t>https://www.tiktok.com/@topgifter99</t>
         </is>
       </c>
       <c r="Z29" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -3549,51 +3465,51 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>12:40:32</t>
+          <t>09:03:46</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>12:40:32.525</t>
+          <t>09:03:46.851</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:32.525-05:00</t>
+          <t>2026-10-14T09:03:46.851-05:00</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>1790271632525</v>
+        <v>1791986626851</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>@ana_tt</t>
+          <t>@jorge_mx</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Ana Torres</t>
+          <t>Jorge Ramírez</t>
         </is>
       </c>
       <c r="J30" s="5" t="n">
-        <v>7300000000001</v>
+        <v>7300000000007</v>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000001demo</t>
+          <t>MS4wLjABAAAA7300000000007demo</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>Saludos desde Colombia 🇨🇴</t>
+          <t>Comparto el directo ahora mismo</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -3603,55 +3519,39 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>3438291620709011879</t>
+          <t>3766596149329558480</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr"/>
-      <c r="P30" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="P30" s="3" t="inlineStr"/>
       <c r="Q30" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R30" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="R30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="inlineStr"/>
-      <c r="U30" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+      <c r="U30" s="3" t="inlineStr"/>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 7, Suscriptor 5, Fan 23, Amigo</t>
+          <t>Nivel de usuario 25</t>
         </is>
       </c>
       <c r="X30" s="4" t="inlineStr"/>
       <c r="Y30" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ana_tt</t>
+          <t>https://www.tiktok.com/@jorge_mx</t>
         </is>
       </c>
       <c r="Z30" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -3661,51 +3561,51 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>12:40:32</t>
+          <t>09:03:47</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>12:40:32.850</t>
+          <t>09:03:47.488</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:32.850-05:00</t>
+          <t>2026-10-14T09:03:47.488-05:00</t>
         </is>
       </c>
       <c r="F31" s="10" t="n">
-        <v>1790271632850</v>
+        <v>1791986627488</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>761</v>
+        <v>657</v>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>@topgifter99</t>
+          <t>@nuria_bcn</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>Carlos Núñez</t>
+          <t>Núria Puig</t>
         </is>
       </c>
       <c r="J31" s="10" t="n">
-        <v>7300000000005</v>
+        <v>7300000000008</v>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000005demo</t>
+          <t>MS4wLjABAAAA7300000000008demo</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>El audio se escucha perfecto</t>
+          <t>Primera vez por aquí, me quedo</t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
@@ -3715,55 +3615,39 @@
       </c>
       <c r="N31" s="9" t="inlineStr">
         <is>
-          <t>2071259094456284111</t>
+          <t>1722329747576025451</t>
         </is>
       </c>
       <c r="O31" s="8" t="inlineStr"/>
-      <c r="P31" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="P31" s="8" t="inlineStr"/>
       <c r="Q31" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="R31" s="8" t="inlineStr"/>
       <c r="S31" s="8" t="inlineStr"/>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="T31" s="8" t="inlineStr"/>
+      <c r="U31" s="8" t="inlineStr"/>
       <c r="V31" s="8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 31, Suscriptor 14, Fan 27, Top gifter 8</t>
+          <t>Nivel de usuario 9</t>
         </is>
       </c>
       <c r="X31" s="9" t="inlineStr"/>
       <c r="Y31" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@topgifter99</t>
+          <t>https://www.tiktok.com/@nuria_bcn</t>
         </is>
       </c>
       <c r="Z31" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -3773,29 +3657,29 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>12:40:33</t>
+          <t>09:03:48</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>12:40:33.803</t>
+          <t>09:03:48.319</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:33.803-05:00</t>
+          <t>2026-10-14T09:03:48.319-05:00</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>1790271633803</v>
+        <v>1791986628319</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>507</v>
+        <v>223</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
@@ -3817,7 +3701,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>Llegué tarde, ¿qué me perdí?</t>
+          <t>Saludos desde Argentina 🇦🇷</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -3827,7 +3711,7 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>2272501176081228170</t>
+          <t>2057829716937173771</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr"/>
@@ -3854,17 +3738,17 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 10, Suscriptor 9, Fan 21, Top gifter 47</t>
+          <t>Nivel de usuario 24, Suscriptor 6, Fan 11, Top gifter 39</t>
         </is>
       </c>
       <c r="X32" s="4" t="inlineStr"/>
@@ -3875,7 +3759,7 @@
       </c>
       <c r="Z32" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -3885,29 +3769,29 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>12:40:34</t>
+          <t>09:03:48</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>12:40:34.352</t>
+          <t>09:03:48.082</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:34.352-05:00</t>
+          <t>2026-10-14T09:03:48.082-05:00</t>
         </is>
       </c>
       <c r="F33" s="10" t="n">
-        <v>1790271634352</v>
+        <v>1791986628082</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>839</v>
+        <v>808</v>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
@@ -3929,7 +3813,7 @@
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>Jajaja no puede ser 😂</t>
+          <t>Muy buena explicación, gracias</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
@@ -3939,7 +3823,7 @@
       </c>
       <c r="N33" s="9" t="inlineStr">
         <is>
-          <t>3666088855741976404</t>
+          <t>1971432268525362540</t>
         </is>
       </c>
       <c r="O33" s="8" t="inlineStr"/>
@@ -3959,12 +3843,12 @@
       <c r="U33" s="8" t="inlineStr"/>
       <c r="V33" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 4, Amigo</t>
+          <t>Nivel de usuario 18, Amigo</t>
         </is>
       </c>
       <c r="X33" s="9" t="inlineStr"/>
@@ -3975,7 +3859,7 @@
       </c>
       <c r="Z33" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -3985,51 +3869,51 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>12:40:35</t>
+          <t>09:03:48</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>12:40:35.112</t>
+          <t>09:03:48.907</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:35.112-05:00</t>
+          <t>2026-10-14T09:03:48.907-05:00</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>1790271635112</v>
+        <v>1791986628907</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>690</v>
+        <v>759</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>@jorge_mx</t>
+          <t>@dani_ar</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Jorge Ramírez</t>
+          <t>Daniela Arias</t>
         </is>
       </c>
       <c r="J34" s="5" t="n">
-        <v>7300000000007</v>
+        <v>7300000000004</v>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000007demo</t>
+          <t>MS4wLjABAAAA7300000000004demo</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>¿Cuál es tu opinión sobre eso?</t>
+          <t>Este tema me interesa mucho</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -4039,7 +3923,7 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>3611961796495703248</t>
+          <t>3597322457871848701</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr"/>
@@ -4055,23 +3939,23 @@
       <c r="U34" s="3" t="inlineStr"/>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 24</t>
+          <t>Nivel de usuario 29</t>
         </is>
       </c>
       <c r="X34" s="4" t="inlineStr"/>
       <c r="Y34" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jorge_mx</t>
+          <t>https://www.tiktok.com/@dani_ar</t>
         </is>
       </c>
       <c r="Z34" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -4081,51 +3965,51 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>12:40:35</t>
+          <t>09:03:49</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>12:40:35.906</t>
+          <t>09:03:49.977</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:35.906-05:00</t>
+          <t>2026-10-14T09:03:49.977-05:00</t>
         </is>
       </c>
       <c r="F35" s="10" t="n">
-        <v>1790271635906</v>
+        <v>1791986629977</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>505</v>
+        <v>478</v>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>@mod_sofia</t>
+          <t>@dani_ar</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>Sofía Moderadora</t>
+          <t>Daniela Arias</t>
         </is>
       </c>
       <c r="J35" s="10" t="n">
-        <v>7300000000006</v>
+        <v>7300000000004</v>
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000006demo</t>
+          <t>MS4wLjABAAAA7300000000004demo</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>¿Cuál es tu opinión sobre eso?</t>
+          <t>Saludos desde Colombia 🇨🇴</t>
         </is>
       </c>
       <c r="M35" s="8" t="inlineStr">
@@ -4135,14 +4019,10 @@
       </c>
       <c r="N35" s="9" t="inlineStr">
         <is>
-          <t>3266391270769400630</t>
-        </is>
-      </c>
-      <c r="O35" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+          <t>1172140269292503465</t>
+        </is>
+      </c>
+      <c r="O35" s="8" t="inlineStr"/>
       <c r="P35" s="8" t="inlineStr"/>
       <c r="Q35" s="8" t="inlineStr">
         <is>
@@ -4155,23 +4035,23 @@
       <c r="U35" s="8" t="inlineStr"/>
       <c r="V35" s="8" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>13</t>
         </is>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 38, Moderador</t>
+          <t>Nivel de usuario 13</t>
         </is>
       </c>
       <c r="X35" s="9" t="inlineStr"/>
       <c r="Y35" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mod_sofia</t>
+          <t>https://www.tiktok.com/@dani_ar</t>
         </is>
       </c>
       <c r="Z35" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -4181,51 +4061,51 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>12:40:36</t>
+          <t>09:03:50</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>12:40:36.376</t>
+          <t>09:03:50.618</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:36.376-05:00</t>
+          <t>2026-10-14T09:03:50.618-05:00</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>1790271636376</v>
+        <v>1791986630618</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>606</v>
+        <v>300</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>@ana_tt</t>
+          <t>@dani_ar</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Ana Torres</t>
+          <t>Daniela Arias</t>
         </is>
       </c>
       <c r="J36" s="5" t="n">
-        <v>7300000000001</v>
+        <v>7300000000004</v>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000001demo</t>
+          <t>MS4wLjABAAAA7300000000004demo</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>¿Cuál es tu opinión sobre eso?</t>
+          <t>Muy buena explicación, gracias</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -4235,55 +4115,39 @@
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>1319366571217819748</t>
+          <t>1409639842662111825</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr"/>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="P36" s="3" t="inlineStr"/>
       <c r="Q36" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="R36" s="3" t="inlineStr"/>
+      <c r="S36" s="3" t="inlineStr"/>
       <c r="T36" s="3" t="inlineStr"/>
-      <c r="U36" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="U36" s="3" t="inlineStr"/>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>39</t>
         </is>
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 18, Suscriptor 15, Fan 8, Amigo</t>
+          <t>Nivel de usuario 39</t>
         </is>
       </c>
       <c r="X36" s="4" t="inlineStr"/>
       <c r="Y36" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ana_tt</t>
+          <t>https://www.tiktok.com/@dani_ar</t>
         </is>
       </c>
       <c r="Z36" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -4293,29 +4157,29 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>12:40:37</t>
+          <t>09:03:50</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>12:40:37.049</t>
+          <t>09:03:50.868</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:37.049-05:00</t>
+          <t>2026-10-14T09:03:50.868-05:00</t>
         </is>
       </c>
       <c r="F37" s="10" t="n">
-        <v>1790271637049</v>
+        <v>1791986630868</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>818</v>
+        <v>501</v>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
@@ -4337,7 +4201,7 @@
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>Jajaja no puede ser 😂</t>
+          <t>Apoyando desde México 🇲🇽</t>
         </is>
       </c>
       <c r="M37" s="8" t="inlineStr">
@@ -4347,7 +4211,7 @@
       </c>
       <c r="N37" s="9" t="inlineStr">
         <is>
-          <t>4608901816714675625</t>
+          <t>618441072735430755</t>
         </is>
       </c>
       <c r="O37" s="8" t="inlineStr"/>
@@ -4374,17 +4238,17 @@
       <c r="T37" s="8" t="inlineStr"/>
       <c r="U37" s="8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="V37" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 1, Suscriptor 17, Fan 23, Amigo</t>
+          <t>Nivel de usuario 10, Suscriptor 3, Fan 19, Amigo</t>
         </is>
       </c>
       <c r="X37" s="9" t="inlineStr"/>
@@ -4395,7 +4259,7 @@
       </c>
       <c r="Z37" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -4405,29 +4269,29 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>12:40:37</t>
+          <t>09:03:51</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>12:40:37.356</t>
+          <t>09:03:51.191</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:37.356-05:00</t>
+          <t>2026-10-14T09:03:51.191-05:00</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>1790271637356</v>
+        <v>1791986631191</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>796</v>
+        <v>645</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
@@ -4449,7 +4313,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>Espectacular como siempre</t>
+          <t>¡Vamos con todo! 🚀</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -4459,7 +4323,7 @@
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>2761430544695589601</t>
+          <t>1481967312970611823</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr"/>
@@ -4479,12 +4343,12 @@
       <c r="U38" s="3" t="inlineStr"/>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>18</t>
         </is>
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 37, Amigo</t>
+          <t>Nivel de usuario 18, Amigo</t>
         </is>
       </c>
       <c r="X38" s="4" t="inlineStr"/>
@@ -4495,7 +4359,7 @@
       </c>
       <c r="Z38" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -4505,51 +4369,51 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>12:40:38</t>
+          <t>09:03:52</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>12:40:38.772</t>
+          <t>09:03:52.168</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:38.772-05:00</t>
+          <t>2026-10-14T09:03:52.168-05:00</t>
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1790271638772</v>
+        <v>1791986632168</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>170</v>
+        <v>312</v>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>@lucia.live</t>
+          <t>@el_marce</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>Lucía Fernández</t>
+          <t>Marcelo Ríos</t>
         </is>
       </c>
       <c r="J39" s="10" t="n">
-        <v>7300000000003</v>
+        <v>7300000000002</v>
       </c>
       <c r="K39" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000003demo</t>
+          <t>MS4wLjABAAAA7300000000002demo</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>Saludos desde Argentina 🇦🇷</t>
+          <t>Jajaja no puede ser 😂</t>
         </is>
       </c>
       <c r="M39" s="8" t="inlineStr">
@@ -4559,7 +4423,7 @@
       </c>
       <c r="N39" s="9" t="inlineStr">
         <is>
-          <t>450740988584291100</t>
+          <t>4530768682015624086</t>
         </is>
       </c>
       <c r="O39" s="8" t="inlineStr"/>
@@ -4570,32 +4434,28 @@
         </is>
       </c>
       <c r="R39" s="8" t="inlineStr"/>
-      <c r="S39" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="S39" s="8" t="inlineStr"/>
       <c r="T39" s="8" t="inlineStr"/>
       <c r="U39" s="8" t="inlineStr"/>
       <c r="V39" s="8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 21, Amigo</t>
+          <t>Nivel de usuario 1</t>
         </is>
       </c>
       <c r="X39" s="9" t="inlineStr"/>
       <c r="Y39" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lucia.live</t>
+          <t>https://www.tiktok.com/@el_marce</t>
         </is>
       </c>
       <c r="Z39" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -4605,51 +4465,51 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>12:40:39</t>
+          <t>09:03:52</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>12:40:39.060</t>
+          <t>09:03:52.211</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:39.060-05:00</t>
+          <t>2026-10-14T09:03:52.211-05:00</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>1790271639060</v>
+        <v>1791986632211</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>706</v>
+        <v>681</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>@nuria_bcn</t>
+          <t>@jorge_mx</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Núria Puig</t>
+          <t>Jorge Ramírez</t>
         </is>
       </c>
       <c r="J40" s="5" t="n">
-        <v>7300000000008</v>
+        <v>7300000000007</v>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000008demo</t>
+          <t>MS4wLjABAAAA7300000000007demo</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>Comparto el directo ahora mismo</t>
+          <t>No me pierdo ninguno 💪</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -4659,7 +4519,7 @@
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>2969690587482889560</t>
+          <t>1117491825687700504</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr"/>
@@ -4675,23 +4535,23 @@
       <c r="U40" s="3" t="inlineStr"/>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 28</t>
+          <t>Nivel de usuario 2</t>
         </is>
       </c>
       <c r="X40" s="4" t="inlineStr"/>
       <c r="Y40" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nuria_bcn</t>
+          <t>https://www.tiktok.com/@jorge_mx</t>
         </is>
       </c>
       <c r="Z40" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -4701,51 +4561,51 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>12:40:39</t>
+          <t>09:03:53</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>12:40:39.488</t>
+          <t>09:03:53.177</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:39.488-05:00</t>
+          <t>2026-10-14T09:03:53.177-05:00</t>
         </is>
       </c>
       <c r="F41" s="10" t="n">
-        <v>1790271639488</v>
+        <v>1791986633177</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>807</v>
+        <v>388</v>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>@dani_ar</t>
+          <t>@nuria_bcn</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>Daniela Arias</t>
+          <t>Núria Puig</t>
         </is>
       </c>
       <c r="J41" s="10" t="n">
-        <v>7300000000004</v>
+        <v>7300000000008</v>
       </c>
       <c r="K41" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000004demo</t>
+          <t>MS4wLjABAAAA7300000000008demo</t>
         </is>
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>¿Puedes repetir eso?</t>
+          <t>¡Vamos con todo! 🚀</t>
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr">
@@ -4755,7 +4615,7 @@
       </c>
       <c r="N41" s="9" t="inlineStr">
         <is>
-          <t>936467814637412841</t>
+          <t>1189045152456428857</t>
         </is>
       </c>
       <c r="O41" s="8" t="inlineStr"/>
@@ -4771,23 +4631,23 @@
       <c r="U41" s="8" t="inlineStr"/>
       <c r="V41" s="8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>38</t>
         </is>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 17</t>
+          <t>Nivel de usuario 38</t>
         </is>
       </c>
       <c r="X41" s="9" t="inlineStr"/>
       <c r="Y41" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dani_ar</t>
+          <t>https://www.tiktok.com/@nuria_bcn</t>
         </is>
       </c>
       <c r="Z41" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -4797,29 +4657,29 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>12:40:40</t>
+          <t>09:03:53</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>12:40:40.073</t>
+          <t>09:03:53.252</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:40.073-05:00</t>
+          <t>2026-10-14T09:03:53.252-05:00</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>1790271640073</v>
+        <v>1791986633252</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>740</v>
+        <v>579</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
@@ -4841,7 +4701,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>No me pierdo ninguno 💪</t>
+          <t>Esto es oro puro</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -4851,7 +4711,7 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>1713396774840491090</t>
+          <t>2559526592515349497</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr"/>
@@ -4878,17 +4738,17 @@
       <c r="T42" s="3" t="inlineStr"/>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>27</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>18</t>
         </is>
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 39, Suscriptor 15, Fan 9, Amigo</t>
+          <t>Nivel de usuario 18, Suscriptor 20, Fan 27, Amigo</t>
         </is>
       </c>
       <c r="X42" s="4" t="inlineStr"/>
@@ -4899,7 +4759,7 @@
       </c>
       <c r="Z42" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -4909,51 +4769,51 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>12:40:40</t>
+          <t>09:03:53</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>12:40:40.620</t>
+          <t>09:03:53.943</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:40.620-05:00</t>
+          <t>2026-10-14T09:03:53.943-05:00</t>
         </is>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1790271640620</v>
+        <v>1791986633943</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>573</v>
+        <v>728</v>
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
-          <t>@nuria_bcn</t>
+          <t>@lucia.live</t>
         </is>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>Núria Puig</t>
+          <t>Lucía Fernández</t>
         </is>
       </c>
       <c r="J43" s="10" t="n">
-        <v>7300000000008</v>
+        <v>7300000000003</v>
       </c>
       <c r="K43" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000008demo</t>
+          <t>MS4wLjABAAAA7300000000003demo</t>
         </is>
       </c>
       <c r="L43" s="9" t="inlineStr">
         <is>
-          <t>¿Haces sorteos?</t>
+          <t>Comparto el directo ahora mismo</t>
         </is>
       </c>
       <c r="M43" s="8" t="inlineStr">
@@ -4963,7 +4823,7 @@
       </c>
       <c r="N43" s="9" t="inlineStr">
         <is>
-          <t>2931312281672212557</t>
+          <t>4253762947352286284</t>
         </is>
       </c>
       <c r="O43" s="8" t="inlineStr"/>
@@ -4974,28 +4834,32 @@
         </is>
       </c>
       <c r="R43" s="8" t="inlineStr"/>
-      <c r="S43" s="8" t="inlineStr"/>
+      <c r="S43" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="T43" s="8" t="inlineStr"/>
       <c r="U43" s="8" t="inlineStr"/>
       <c r="V43" s="8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 22</t>
+          <t>Nivel de usuario 32, Amigo</t>
         </is>
       </c>
       <c r="X43" s="9" t="inlineStr"/>
       <c r="Y43" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nuria_bcn</t>
+          <t>https://www.tiktok.com/@lucia.live</t>
         </is>
       </c>
       <c r="Z43" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -5005,51 +4869,51 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>12:40:41</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>12:40:41.108</t>
+          <t>09:03:54.354</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:41.108-05:00</t>
+          <t>2026-10-14T09:03:54.354-05:00</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>1790271641108</v>
+        <v>1791986634354</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>504</v>
+        <v>891</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>@dani_ar</t>
+          <t>@nuria_bcn</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Daniela Arias</t>
+          <t>Núria Puig</t>
         </is>
       </c>
       <c r="J44" s="5" t="n">
-        <v>7300000000004</v>
+        <v>7300000000008</v>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000004demo</t>
+          <t>MS4wLjABAAAA7300000000008demo</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>Espectacular como siempre</t>
+          <t>¡Qué buen contenido! 🔥</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -5059,7 +4923,7 @@
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>4476303233328903795</t>
+          <t>1110607067275264533</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr"/>
@@ -5086,12 +4950,12 @@
       <c r="X44" s="4" t="inlineStr"/>
       <c r="Y44" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dani_ar</t>
+          <t>https://www.tiktok.com/@nuria_bcn</t>
         </is>
       </c>
       <c r="Z44" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -5101,29 +4965,29 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>12:40:41</t>
+          <t>09:03:55</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>12:40:41.153</t>
+          <t>09:03:55.282</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:41.153-05:00</t>
+          <t>2026-10-14T09:03:55.282-05:00</t>
         </is>
       </c>
       <c r="F45" s="10" t="n">
-        <v>1790271641153</v>
+        <v>1791986635282</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>733</v>
+        <v>440</v>
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
@@ -5155,7 +5019,7 @@
       </c>
       <c r="N45" s="9" t="inlineStr">
         <is>
-          <t>1776479404470311644</t>
+          <t>995832988879597539</t>
         </is>
       </c>
       <c r="O45" s="8" t="inlineStr"/>
@@ -5171,12 +5035,12 @@
       <c r="U45" s="8" t="inlineStr"/>
       <c r="V45" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 10</t>
+          <t>Nivel de usuario 26</t>
         </is>
       </c>
       <c r="X45" s="9" t="inlineStr"/>
@@ -5187,7 +5051,7 @@
       </c>
       <c r="Z45" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -5197,51 +5061,51 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>12:40:42</t>
+          <t>09:03:55</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>12:40:42.069</t>
+          <t>09:03:55.903</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:42.069-05:00</t>
+          <t>2026-10-14T09:03:55.903-05:00</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>1790271642069</v>
+        <v>1791986635903</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>437</v>
+        <v>130</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>@jorge_mx</t>
+          <t>@mod_sofia</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Jorge Ramírez</t>
+          <t>Sofía Moderadora</t>
         </is>
       </c>
       <c r="J46" s="5" t="n">
-        <v>7300000000007</v>
+        <v>7300000000006</v>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000007demo</t>
+          <t>MS4wLjABAAAA7300000000006demo</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>¿Cuál es tu opinión sobre eso?</t>
+          <t>Apoyando desde México 🇲🇽</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -5251,10 +5115,14 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>795494410714991409</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr"/>
+          <t>2732253394587722848</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="P46" s="3" t="inlineStr"/>
       <c r="Q46" s="3" t="inlineStr">
         <is>
@@ -5272,18 +5140,18 @@
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 30</t>
+          <t>Nivel de usuario 30, Moderador</t>
         </is>
       </c>
       <c r="X46" s="4" t="inlineStr"/>
       <c r="Y46" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jorge_mx</t>
+          <t>https://www.tiktok.com/@mod_sofia</t>
         </is>
       </c>
       <c r="Z46" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -5293,51 +5161,51 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>12:40:42</t>
+          <t>09:03:56</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>12:40:42.175</t>
+          <t>09:03:56.404</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:42.175-05:00</t>
+          <t>2026-10-14T09:03:56.404-05:00</t>
         </is>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1790271642175</v>
+        <v>1791986636404</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>675</v>
+        <v>304</v>
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
-          <t>@nuria_bcn</t>
+          <t>@mod_sofia</t>
         </is>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>Núria Puig</t>
+          <t>Sofía Moderadora</t>
         </is>
       </c>
       <c r="J47" s="10" t="n">
-        <v>7300000000008</v>
+        <v>7300000000006</v>
       </c>
       <c r="K47" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000008demo</t>
+          <t>MS4wLjABAAAA7300000000006demo</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr">
         <is>
-          <t>¿Se puede participar?</t>
+          <t>Apoyando desde México 🇲🇽</t>
         </is>
       </c>
       <c r="M47" s="8" t="inlineStr">
@@ -5347,10 +5215,14 @@
       </c>
       <c r="N47" s="9" t="inlineStr">
         <is>
-          <t>3980317296947038004</t>
-        </is>
-      </c>
-      <c r="O47" s="8" t="inlineStr"/>
+          <t>3732331053197373403</t>
+        </is>
+      </c>
+      <c r="O47" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="P47" s="8" t="inlineStr"/>
       <c r="Q47" s="8" t="inlineStr">
         <is>
@@ -5363,23 +5235,23 @@
       <c r="U47" s="8" t="inlineStr"/>
       <c r="V47" s="8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 24</t>
+          <t>Nivel de usuario 9, Moderador</t>
         </is>
       </c>
       <c r="X47" s="9" t="inlineStr"/>
       <c r="Y47" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nuria_bcn</t>
+          <t>https://www.tiktok.com/@mod_sofia</t>
         </is>
       </c>
       <c r="Z47" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -5389,29 +5261,29 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>12:40:43</t>
+          <t>09:03:56</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>12:40:43.607</t>
+          <t>09:03:56.536</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:43.607-05:00</t>
+          <t>2026-10-14T09:03:56.536-05:00</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>1790271643607</v>
+        <v>1791986636536</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>132</v>
+        <v>687</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
@@ -5433,7 +5305,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>¿Cuándo es el próximo directo?</t>
+          <t>Llegué tarde, ¿qué me perdí?</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -5443,7 +5315,7 @@
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>1311202678242044600</t>
+          <t>4413854400672974677</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr"/>
@@ -5459,12 +5331,12 @@
       <c r="U48" s="3" t="inlineStr"/>
       <c r="V48" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 6</t>
+          <t>Nivel de usuario 22</t>
         </is>
       </c>
       <c r="X48" s="4" t="inlineStr"/>
@@ -5475,7 +5347,7 @@
       </c>
       <c r="Z48" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -5485,51 +5357,51 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>12:40:43</t>
+          <t>09:03:57</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>12:40:43.672</t>
+          <t>09:03:57.662</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:43.672-05:00</t>
+          <t>2026-10-14T09:03:57.662-05:00</t>
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1790271643672</v>
+        <v>1791986637662</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>865</v>
+        <v>389</v>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>@nuria_bcn</t>
+          <t>@ana_tt</t>
         </is>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
-          <t>Núria Puig</t>
+          <t>Ana Torres</t>
         </is>
       </c>
       <c r="J49" s="10" t="n">
-        <v>7300000000008</v>
+        <v>7300000000001</v>
       </c>
       <c r="K49" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000008demo</t>
+          <t>MS4wLjABAAAA7300000000001demo</t>
         </is>
       </c>
       <c r="L49" s="9" t="inlineStr">
         <is>
-          <t>¿Cuándo es el próximo directo?</t>
+          <t>¡Vamos con todo! 🚀</t>
         </is>
       </c>
       <c r="M49" s="8" t="inlineStr">
@@ -5539,39 +5411,55 @@
       </c>
       <c r="N49" s="9" t="inlineStr">
         <is>
-          <t>3592010413354381990</t>
+          <t>3035874907830975841</t>
         </is>
       </c>
       <c r="O49" s="8" t="inlineStr"/>
-      <c r="P49" s="8" t="inlineStr"/>
+      <c r="P49" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q49" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R49" s="8" t="inlineStr"/>
-      <c r="S49" s="8" t="inlineStr"/>
+      <c r="R49" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S49" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="T49" s="8" t="inlineStr"/>
-      <c r="U49" s="8" t="inlineStr"/>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="V49" s="8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 22</t>
+          <t>Nivel de usuario 25, Suscriptor 8, Fan 24, Amigo</t>
         </is>
       </c>
       <c r="X49" s="9" t="inlineStr"/>
       <c r="Y49" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nuria_bcn</t>
+          <t>https://www.tiktok.com/@ana_tt</t>
         </is>
       </c>
       <c r="Z49" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -5581,51 +5469,51 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>12:40:44</t>
+          <t>09:03:58</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>12:40:44.541</t>
+          <t>09:03:58.096</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:44.541-05:00</t>
+          <t>2026-10-14T09:03:58.096-05:00</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>1790271644541</v>
+        <v>1791986638096</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>336</v>
+        <v>673</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>@jorge_mx</t>
+          <t>@topgifter99</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>Jorge Ramírez</t>
+          <t>Carlos Núñez</t>
         </is>
       </c>
       <c r="J50" s="5" t="n">
-        <v>7300000000007</v>
+        <v>7300000000005</v>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000007demo</t>
+          <t>MS4wLjABAAAA7300000000005demo</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>Espectacular como siempre</t>
+          <t>¿Cuál es tu opinión sobre eso?</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -5635,39 +5523,55 @@
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>1799202265934880154</t>
+          <t>2038000934791391771</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr"/>
-      <c r="P50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="S50" s="3" t="inlineStr"/>
-      <c r="T50" s="3" t="inlineStr"/>
-      <c r="U50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="V50" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33</t>
         </is>
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 37</t>
+          <t>Nivel de usuario 33, Suscriptor 9, Fan 25, Top gifter 5</t>
         </is>
       </c>
       <c r="X50" s="4" t="inlineStr"/>
       <c r="Y50" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jorge_mx</t>
+          <t>https://www.tiktok.com/@topgifter99</t>
         </is>
       </c>
       <c r="Z50" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -5677,51 +5581,51 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>12:40:44</t>
+          <t>09:03:58</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>12:40:44.893</t>
+          <t>09:03:58.724</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:44.893-05:00</t>
+          <t>2026-10-14T09:03:58.724-05:00</t>
         </is>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1790271644893</v>
+        <v>1791986638724</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>315</v>
+        <v>770</v>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>@ana_tt</t>
+          <t>@nuria_bcn</t>
         </is>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
-          <t>Ana Torres</t>
+          <t>Núria Puig</t>
         </is>
       </c>
       <c r="J51" s="10" t="n">
-        <v>7300000000001</v>
+        <v>7300000000008</v>
       </c>
       <c r="K51" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000001demo</t>
+          <t>MS4wLjABAAAA7300000000008demo</t>
         </is>
       </c>
       <c r="L51" s="9" t="inlineStr">
         <is>
-          <t>Comparto el directo ahora mismo</t>
+          <t>Llegué tarde, ¿qué me perdí?</t>
         </is>
       </c>
       <c r="M51" s="8" t="inlineStr">
@@ -5731,55 +5635,39 @@
       </c>
       <c r="N51" s="9" t="inlineStr">
         <is>
-          <t>3344399625085995813</t>
+          <t>267904142646424231</t>
         </is>
       </c>
       <c r="O51" s="8" t="inlineStr"/>
-      <c r="P51" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="P51" s="8" t="inlineStr"/>
       <c r="Q51" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R51" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S51" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="R51" s="8" t="inlineStr"/>
+      <c r="S51" s="8" t="inlineStr"/>
       <c r="T51" s="8" t="inlineStr"/>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+      <c r="U51" s="8" t="inlineStr"/>
       <c r="V51" s="8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 20, Suscriptor 5, Fan 24, Amigo</t>
+          <t>Nivel de usuario 13</t>
         </is>
       </c>
       <c r="X51" s="9" t="inlineStr"/>
       <c r="Y51" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ana_tt</t>
+          <t>https://www.tiktok.com/@nuria_bcn</t>
         </is>
       </c>
       <c r="Z51" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -5789,51 +5677,51 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>12:40:44</t>
+          <t>09:03:59</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>12:40:44.708</t>
+          <t>09:03:59.745</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:44.708-05:00</t>
+          <t>2026-10-14T09:03:59.745-05:00</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>1790271644708</v>
+        <v>1791986639745</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>831</v>
+        <v>352</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>@nuria_bcn</t>
+          <t>@mod_sofia</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>Núria Puig</t>
+          <t>Sofía Moderadora</t>
         </is>
       </c>
       <c r="J52" s="5" t="n">
-        <v>7300000000008</v>
+        <v>7300000000006</v>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000008demo</t>
+          <t>MS4wLjABAAAA7300000000006demo</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>¿Cuál es tu opinión sobre eso?</t>
+          <t>¿Vas a subir el resumen?</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -5843,10 +5731,14 @@
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>2150276437516202605</t>
-        </is>
-      </c>
-      <c r="O52" s="3" t="inlineStr"/>
+          <t>575835412748428310</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="P52" s="3" t="inlineStr"/>
       <c r="Q52" s="3" t="inlineStr">
         <is>
@@ -5859,23 +5751,23 @@
       <c r="U52" s="3" t="inlineStr"/>
       <c r="V52" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 14</t>
+          <t>Nivel de usuario 9, Moderador</t>
         </is>
       </c>
       <c r="X52" s="4" t="inlineStr"/>
       <c r="Y52" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nuria_bcn</t>
+          <t>https://www.tiktok.com/@mod_sofia</t>
         </is>
       </c>
       <c r="Z52" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -5885,51 +5777,51 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>12:40:45</t>
+          <t>09:04:00</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>12:40:45.385</t>
+          <t>09:04:00.256</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:45.385-05:00</t>
+          <t>2026-10-14T09:04:00.256-05:00</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>1790271645385</v>
+        <v>1791986640256</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>881</v>
+        <v>652</v>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>@topgifter99</t>
+          <t>@nuria_bcn</t>
         </is>
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>Carlos Núñez</t>
+          <t>Núria Puig</t>
         </is>
       </c>
       <c r="J53" s="10" t="n">
-        <v>7300000000005</v>
+        <v>7300000000008</v>
       </c>
       <c r="K53" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000005demo</t>
+          <t>MS4wLjABAAAA7300000000008demo</t>
         </is>
       </c>
       <c r="L53" s="9" t="inlineStr">
         <is>
-          <t>Ya te seguí hace tiempo</t>
+          <t>¿Haces sorteos?</t>
         </is>
       </c>
       <c r="M53" s="8" t="inlineStr">
@@ -5939,55 +5831,39 @@
       </c>
       <c r="N53" s="9" t="inlineStr">
         <is>
-          <t>3195651231734301431</t>
+          <t>101402315214889645</t>
         </is>
       </c>
       <c r="O53" s="8" t="inlineStr"/>
-      <c r="P53" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="P53" s="8" t="inlineStr"/>
       <c r="Q53" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R53" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="R53" s="8" t="inlineStr"/>
       <c r="S53" s="8" t="inlineStr"/>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="T53" s="8" t="inlineStr"/>
+      <c r="U53" s="8" t="inlineStr"/>
       <c r="V53" s="8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 19, Suscriptor 5, Fan 14, Top gifter 13</t>
+          <t>Nivel de usuario 12</t>
         </is>
       </c>
       <c r="X53" s="9" t="inlineStr"/>
       <c r="Y53" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@topgifter99</t>
+          <t>https://www.tiktok.com/@nuria_bcn</t>
         </is>
       </c>
       <c r="Z53" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -5997,51 +5873,51 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>12:40:46</t>
+          <t>09:04:01</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>12:40:46.115</t>
+          <t>09:04:01.149</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:46.115-05:00</t>
+          <t>2026-10-14T09:04:01.149-05:00</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>1790271646115</v>
+        <v>1791986641149</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>617</v>
+        <v>326</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>@el_marce</t>
+          <t>@mod_sofia</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>Marcelo Ríos</t>
+          <t>Sofía Moderadora</t>
         </is>
       </c>
       <c r="J54" s="5" t="n">
-        <v>7300000000002</v>
+        <v>7300000000006</v>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000002demo</t>
+          <t>MS4wLjABAAAA7300000000006demo</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>Esto es oro puro</t>
+          <t>Saludos desde Argentina 🇦🇷</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -6051,10 +5927,14 @@
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>317203485536480140</t>
-        </is>
-      </c>
-      <c r="O54" s="3" t="inlineStr"/>
+          <t>123674043995102483</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="P54" s="3" t="inlineStr"/>
       <c r="Q54" s="3" t="inlineStr">
         <is>
@@ -6067,23 +5947,23 @@
       <c r="U54" s="3" t="inlineStr"/>
       <c r="V54" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 6</t>
+          <t>Nivel de usuario 35, Moderador</t>
         </is>
       </c>
       <c r="X54" s="4" t="inlineStr"/>
       <c r="Y54" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@el_marce</t>
+          <t>https://www.tiktok.com/@mod_sofia</t>
         </is>
       </c>
       <c r="Z54" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -6093,51 +5973,51 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>12:40:47</t>
+          <t>09:04:01</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>12:40:47.190</t>
+          <t>09:04:01.630</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:47.190-05:00</t>
+          <t>2026-10-14T09:04:01.630-05:00</t>
         </is>
       </c>
       <c r="F55" s="10" t="n">
-        <v>1790271647190</v>
+        <v>1791986641630</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>196</v>
+        <v>615</v>
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
-          <t>@topgifter99</t>
+          <t>@lucia.live</t>
         </is>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>Carlos Núñez</t>
+          <t>Lucía Fernández</t>
         </is>
       </c>
       <c r="J55" s="10" t="n">
-        <v>7300000000005</v>
+        <v>7300000000003</v>
       </c>
       <c r="K55" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000005demo</t>
+          <t>MS4wLjABAAAA7300000000003demo</t>
         </is>
       </c>
       <c r="L55" s="9" t="inlineStr">
         <is>
-          <t>¡Hola a todos! 👋</t>
+          <t>¿De qué trata el directo hoy?</t>
         </is>
       </c>
       <c r="M55" s="8" t="inlineStr">
@@ -6147,55 +6027,43 @@
       </c>
       <c r="N55" s="9" t="inlineStr">
         <is>
-          <t>759396730649508752</t>
+          <t>429091002416877500</t>
         </is>
       </c>
       <c r="O55" s="8" t="inlineStr"/>
-      <c r="P55" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="P55" s="8" t="inlineStr"/>
       <c r="Q55" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R55" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S55" s="8" t="inlineStr"/>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
+      <c r="R55" s="8" t="inlineStr"/>
+      <c r="S55" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr"/>
+      <c r="U55" s="8" t="inlineStr"/>
+      <c r="V55" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 28, Suscriptor 20, Fan 15, Top gifter 8</t>
+          <t>Nivel de usuario 15, Amigo</t>
         </is>
       </c>
       <c r="X55" s="9" t="inlineStr"/>
       <c r="Y55" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@topgifter99</t>
+          <t>https://www.tiktok.com/@lucia.live</t>
         </is>
       </c>
       <c r="Z55" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -6205,51 +6073,51 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>12:40:47</t>
+          <t>09:04:02</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>12:40:47.077</t>
+          <t>09:04:02.623</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:47.077-05:00</t>
+          <t>2026-10-14T09:04:02.623-05:00</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>1790271647077</v>
+        <v>1791986642623</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>885</v>
+        <v>500</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>@topgifter99</t>
+          <t>@mod_sofia</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>Carlos Núñez</t>
+          <t>Sofía Moderadora</t>
         </is>
       </c>
       <c r="J56" s="5" t="n">
-        <v>7300000000005</v>
+        <v>7300000000006</v>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000005demo</t>
+          <t>MS4wLjABAAAA7300000000006demo</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>Saludos desde Argentina 🇦🇷</t>
+          <t>¿Puedes repetir eso?</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -6259,36 +6127,24 @@
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>253401599536175721</t>
-        </is>
-      </c>
-      <c r="O56" s="3" t="inlineStr"/>
-      <c r="P56" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+          <t>301155621054887098</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr"/>
       <c r="Q56" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R56" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="R56" s="3" t="inlineStr"/>
       <c r="S56" s="3" t="inlineStr"/>
-      <c r="T56" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="U56" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr"/>
       <c r="V56" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -6296,18 +6152,18 @@
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 5, Suscriptor 9, Fan 20, Top gifter 3</t>
+          <t>Nivel de usuario 5, Moderador</t>
         </is>
       </c>
       <c r="X56" s="4" t="inlineStr"/>
       <c r="Y56" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@topgifter99</t>
+          <t>https://www.tiktok.com/@mod_sofia</t>
         </is>
       </c>
       <c r="Z56" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -6317,51 +6173,51 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>12:40:48</t>
+          <t>09:04:02</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>12:40:48.074</t>
+          <t>09:04:02.886</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:48.074-05:00</t>
+          <t>2026-10-14T09:04:02.886-05:00</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>1790271648074</v>
+        <v>1791986642886</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>480</v>
+        <v>850</v>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>@mod_sofia</t>
+          <t>@dani_ar</t>
         </is>
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>Sofía Moderadora</t>
+          <t>Daniela Arias</t>
         </is>
       </c>
       <c r="J57" s="10" t="n">
-        <v>7300000000006</v>
+        <v>7300000000004</v>
       </c>
       <c r="K57" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000006demo</t>
+          <t>MS4wLjABAAAA7300000000004demo</t>
         </is>
       </c>
       <c r="L57" s="9" t="inlineStr">
         <is>
-          <t>¡Vamos con todo! 🚀</t>
+          <t>Esto es oro puro</t>
         </is>
       </c>
       <c r="M57" s="8" t="inlineStr">
@@ -6371,14 +6227,10 @@
       </c>
       <c r="N57" s="9" t="inlineStr">
         <is>
-          <t>135541630275478860</t>
-        </is>
-      </c>
-      <c r="O57" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+          <t>2547665074183160039</t>
+        </is>
+      </c>
+      <c r="O57" s="8" t="inlineStr"/>
       <c r="P57" s="8" t="inlineStr"/>
       <c r="Q57" s="8" t="inlineStr">
         <is>
@@ -6391,23 +6243,23 @@
       <c r="U57" s="8" t="inlineStr"/>
       <c r="V57" s="8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 26, Moderador</t>
+          <t>Nivel de usuario 25</t>
         </is>
       </c>
       <c r="X57" s="9" t="inlineStr"/>
       <c r="Y57" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mod_sofia</t>
+          <t>https://www.tiktok.com/@dani_ar</t>
         </is>
       </c>
       <c r="Z57" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -6417,51 +6269,51 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>12:40:48</t>
+          <t>09:04:04</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>12:40:48.673</t>
+          <t>09:04:04.309</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:48.673-05:00</t>
+          <t>2026-10-14T09:04:04.309-05:00</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>1790271648673</v>
+        <v>1791986644309</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>328</v>
+        <v>227</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>@nuria_bcn</t>
+          <t>@jorge_mx</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>Núria Puig</t>
+          <t>Jorge Ramírez</t>
         </is>
       </c>
       <c r="J58" s="5" t="n">
-        <v>7300000000008</v>
+        <v>7300000000007</v>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000008demo</t>
+          <t>MS4wLjABAAAA7300000000007demo</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>Espectacular como siempre</t>
+          <t>No me pierdo ninguno 💪</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -6471,7 +6323,7 @@
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>101925385092438992</t>
+          <t>2869407613190661233</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr"/>
@@ -6487,23 +6339,23 @@
       <c r="U58" s="3" t="inlineStr"/>
       <c r="V58" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 6</t>
+          <t>Nivel de usuario 15</t>
         </is>
       </c>
       <c r="X58" s="4" t="inlineStr"/>
       <c r="Y58" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nuria_bcn</t>
+          <t>https://www.tiktok.com/@jorge_mx</t>
         </is>
       </c>
       <c r="Z58" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -6513,29 +6365,29 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>12:40:48</t>
+          <t>09:04:05</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>12:40:48.844</t>
+          <t>09:04:05.142</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:48.844-05:00</t>
+          <t>2026-10-14T09:04:05.142-05:00</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>1790271648844</v>
+        <v>1791986645142</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>761</v>
+        <v>231</v>
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
@@ -6557,7 +6409,7 @@
       </c>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>¿Se puede participar?</t>
+          <t>Comparto el directo ahora mismo</t>
         </is>
       </c>
       <c r="M59" s="8" t="inlineStr">
@@ -6567,7 +6419,7 @@
       </c>
       <c r="N59" s="9" t="inlineStr">
         <is>
-          <t>3911338500037799170</t>
+          <t>93719867976986141</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr"/>
@@ -6583,12 +6435,12 @@
       <c r="U59" s="8" t="inlineStr"/>
       <c r="V59" s="8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 34</t>
+          <t>Nivel de usuario 9</t>
         </is>
       </c>
       <c r="X59" s="9" t="inlineStr"/>
@@ -6599,7 +6451,7 @@
       </c>
       <c r="Z59" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -6609,51 +6461,51 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>12:40:49</t>
+          <t>09:04:05</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>12:40:49.931</t>
+          <t>09:04:05.431</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:49.931-05:00</t>
+          <t>2026-10-14T09:04:05.431-05:00</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>1790271649931</v>
+        <v>1791986645431</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>126</v>
+        <v>447</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>@nuria_bcn</t>
+          <t>@ana_tt</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>Núria Puig</t>
+          <t>Ana Torres</t>
         </is>
       </c>
       <c r="J60" s="5" t="n">
-        <v>7300000000008</v>
+        <v>7300000000001</v>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000008demo</t>
+          <t>MS4wLjABAAAA7300000000001demo</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>Comparto el directo ahora mismo</t>
+          <t>¿De qué trata el directo hoy?</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -6663,39 +6515,55 @@
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>518892382727321531</t>
+          <t>1539327743668906650</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr"/>
-      <c r="P60" s="3" t="inlineStr"/>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R60" s="3" t="inlineStr"/>
-      <c r="S60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="T60" s="3" t="inlineStr"/>
-      <c r="U60" s="3" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="V60" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="W60" s="4" t="inlineStr">
         <is>
-          <t>Nivel de usuario 15</t>
+          <t>Nivel de usuario 27, Suscriptor 11, Fan 30, Amigo</t>
         </is>
       </c>
       <c r="X60" s="4" t="inlineStr"/>
       <c r="Y60" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nuria_bcn</t>
+          <t>https://www.tiktok.com/@ana_tt</t>
         </is>
       </c>
       <c r="Z60" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -6705,51 +6573,51 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>12:40:50</t>
+          <t>09:04:06</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>12:40:50.347</t>
+          <t>09:04:06.112</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24T12:40:50.347-05:00</t>
+          <t>2026-10-14T09:04:06.112-05:00</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>1790271650347</v>
+        <v>1791986646112</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>460</v>
+        <v>347</v>
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>@topgifter99</t>
+          <t>@lucia.live</t>
         </is>
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>Carlos Núñez</t>
+          <t>Lucía Fernández</t>
         </is>
       </c>
       <c r="J61" s="10" t="n">
-        <v>7300000000005</v>
+        <v>7300000000003</v>
       </c>
       <c r="K61" s="9" t="inlineStr">
         <is>
-          <t>MS4wLjABAAAA7300000000005demo</t>
+          <t>MS4wLjABAAAA7300000000003demo</t>
         </is>
       </c>
       <c r="L61" s="9" t="inlineStr">
         <is>
-          <t>¡Hola a todos! 👋</t>
+          <t>¿Se puede participar?</t>
         </is>
       </c>
       <c r="M61" s="8" t="inlineStr">
@@ -6759,55 +6627,43 @@
       </c>
       <c r="N61" s="9" t="inlineStr">
         <is>
-          <t>6654018038991052</t>
+          <t>3337108244667789494</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr"/>
-      <c r="P61" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="P61" s="8" t="inlineStr"/>
       <c r="Q61" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="R61" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S61" s="8" t="inlineStr"/>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="R61" s="8" t="inlineStr"/>
+      <c r="S61" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr"/>
+      <c r="U61" s="8" t="inlineStr"/>
       <c r="V61" s="8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>34</t>
         </is>
       </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
-          <t>Nivel de usuario 40, Suscriptor 12, Fan 4, Top gifter 34</t>
+          <t>Nivel de usuario 34, Amigo</t>
         </is>
       </c>
       <c r="X61" s="9" t="inlineStr"/>
       <c r="Y61" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@topgifter99</t>
+          <t>https://www.tiktok.com/@lucia.live</t>
         </is>
       </c>
       <c r="Z61" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -6977,12 +6833,12 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>12:40:18.107</t>
+          <t>09:03:36.193</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>12:40:49.931</t>
+          <t>09:04:00.256</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -7002,130 +6858,118 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>@topgifter99</t>
+          <t>@jorge_mx</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Carlos Núñez</t>
+          <t>Jorge Ramírez</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>7300000000005</v>
+        <v>7300000000007</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>12:40:19.001</t>
+          <t>09:03:31.808</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>12:40:50.347</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+          <t>09:04:05.142</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr"/>
       <c r="H3" s="8" t="inlineStr"/>
       <c r="I3" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@topgifter99</t>
+          <t>https://www.tiktok.com/@jorge_mx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>@ana_tt</t>
+          <t>@lucia.live</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Ana Torres</t>
+          <t>Lucía Fernández</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>7300000000001</v>
+        <v>7300000000003</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>10</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>12:40:20.069</t>
+          <t>09:03:32.886</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>12:40:44.893</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+          <t>09:04:06.112</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr"/>
       <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+      <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ana_tt</t>
+          <t>https://www.tiktok.com/@lucia.live</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>@jorge_mx</t>
+          <t>@mod_sofia</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Jorge Ramírez</t>
+          <t>Sofía Moderadora</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>7300000000007</v>
+        <v>7300000000006</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>12:40:21.988</t>
+          <t>09:03:33.081</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>12:40:48.844</t>
+          <t>09:04:02.623</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -7134,35 +6978,35 @@
       <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jorge_mx</t>
+          <t>https://www.tiktok.com/@mod_sofia</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>@lucia.live</t>
+          <t>@dani_ar</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Lucía Fernández</t>
+          <t>Daniela Arias</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>7300000000003</v>
+        <v>7300000000004</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>12:40:26.437</t>
+          <t>09:03:35.223</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>12:40:38.772</t>
+          <t>09:04:02.886</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -7175,125 +7019,137 @@
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lucia.live</t>
+          <t>https://www.tiktok.com/@dani_ar</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>@dani_ar</t>
+          <t>@topgifter99</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Daniela Arias</t>
+          <t>Carlos Núñez</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>7300000000004</v>
+        <v>7300000000005</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>12:40:17.640</t>
+          <t>09:03:34.078</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>12:40:41.108</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr"/>
+          <t>09:03:58.096</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="H7" s="8" t="inlineStr"/>
       <c r="I7" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dani_ar</t>
+          <t>https://www.tiktok.com/@topgifter99</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>@el_marce</t>
+          <t>@ana_tt</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Marcelo Ríos</t>
+          <t>Ana Torres</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>7300000000002</v>
+        <v>7300000000001</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>12:40:21.007</t>
+          <t>09:03:50.868</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>12:40:46.115</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
+          <t>09:04:05.431</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@el_marce</t>
+          <t>https://www.tiktok.com/@ana_tt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>@mod_sofia</t>
+          <t>@el_marce</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Sofía Moderadora</t>
+          <t>Marcelo Ríos</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>7300000000006</v>
+        <v>7300000000002</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>12:40:28.275</t>
+          <t>09:03:37.110</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>12:40:48.074</t>
+          <t>09:03:52.168</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="H9" s="8" t="inlineStr"/>
       <c r="I9" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -7302,7 +7158,7 @@
       <c r="J9" s="8" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mod_sofia</t>
+          <t>https://www.tiktok.com/@el_marce</t>
         </is>
       </c>
     </row>
@@ -7425,12 +7281,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>12:40:51.581</t>
+          <t>09:03:34.849</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -7458,22 +7314,22 @@
         <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>3144321141345860490</t>
+          <t>4287176683831971114</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -7483,12 +7339,12 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>12:40:52.311</t>
+          <t>09:03:36.980</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
@@ -7526,12 +7382,12 @@
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>33072628538438907</t>
+          <t>1976652229942308814</t>
         </is>
       </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -7541,37 +7397,37 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>12:40:52.744</t>
+          <t>09:03:38.814</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>@dani_ar</t>
+          <t>@mod_sofia</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Daniela Arias</t>
+          <t>Sofía Moderadora</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>7300000000004</v>
+        <v>7300000000006</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Corazón</t>
+          <t>Galaxia</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>5509</v>
+        <v>5587</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1</v>
@@ -7580,16 +7436,16 @@
         <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>3569968890215336315</t>
+          <t>2507320654596425823</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -7599,37 +7455,37 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>12:40:53.199</t>
+          <t>09:03:40.902</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>@ana_tt</t>
+          <t>@lucia.live</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Ana Torres</t>
+          <t>Lucía Fernández</t>
         </is>
       </c>
       <c r="F5" s="10" t="n">
-        <v>7300000000001</v>
+        <v>7300000000003</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>Galaxia</t>
+          <t>Corazón</t>
         </is>
       </c>
       <c r="H5" s="7" t="n">
-        <v>5587</v>
+        <v>5509</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>1</v>
@@ -7638,16 +7494,16 @@
         <v>1</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>2747405294268128368</t>
+          <t>3632833276955004353</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -7657,55 +7513,55 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>12:40:53.776</t>
+          <t>09:03:43.301</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>@dani_ar</t>
+          <t>@lucia.live</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Daniela Arias</t>
+          <t>Lucía Fernández</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>7300000000004</v>
+        <v>7300000000003</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Galaxia</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>5827</v>
+        <v>5587</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>362425292875144926</t>
+          <t>3885735753447087461</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -7715,34 +7571,34 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>12:40:54.308</t>
+          <t>09:03:45.554</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>@el_marce</t>
+          <t>@topgifter99</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Marcelo Ríos</t>
+          <t>Carlos Núñez</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>7300000000002</v>
+        <v>7300000000005</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Rosa</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>5655</v>
+        <v>5827</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>1</v>
@@ -7758,12 +7614,12 @@
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>1595313928079361612</t>
+          <t>596790994850859135</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -7773,37 +7629,37 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>12:40:55.058</t>
+          <t>09:03:47.570</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>@nuria_bcn</t>
+          <t>@el_marce</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Núria Puig</t>
+          <t>Marcelo Ríos</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>7300000000008</v>
+        <v>7300000000002</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Corazón</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>5509</v>
+        <v>5827</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>1</v>
@@ -7812,16 +7668,16 @@
         <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>2240701950100048857</t>
+          <t>3018527893633705749</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -7831,55 +7687,55 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>12:40:55.465</t>
+          <t>09:03:49.667</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>@ana_tt</t>
+          <t>@topgifter99</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Ana Torres</t>
+          <t>Carlos Núñez</t>
         </is>
       </c>
       <c r="F9" s="10" t="n">
-        <v>7300000000001</v>
+        <v>7300000000005</v>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Galaxia</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
-        <v>5587</v>
+        <v>5827</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>2151099671923462675</t>
+          <t>3947865572469480762</t>
         </is>
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -7889,55 +7745,55 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>12:40:56.000</t>
+          <t>09:03:51.837</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>@mod_sofia</t>
+          <t>@lucia.live</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Sofía Moderadora</t>
+          <t>Lucía Fernández</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>7300000000006</v>
+        <v>7300000000003</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Rosa</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>5827</v>
+        <v>5655</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>4534707268026555997</t>
+          <t>579959525684816255</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -7947,26 +7803,26 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>12:40:56.530</t>
+          <t>09:03:53.831</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>@dani_ar</t>
+          <t>@ana_tt</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Daniela Arias</t>
+          <t>Ana Torres</t>
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>7300000000004</v>
+        <v>7300000000001</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
@@ -7980,22 +7836,22 @@
         <v>1</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>3358052730166723314</t>
+          <t>3141004027285322007</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -8005,55 +7861,55 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>12:40:56.878</t>
+          <t>09:03:56.034</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>@ana_tt</t>
+          <t>@topgifter99</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Ana Torres</t>
+          <t>Carlos Núñez</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>7300000000001</v>
+        <v>7300000000005</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Rosa</t>
+          <t>Galaxia</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>5655</v>
+        <v>5587</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>3720240260034376501</t>
+          <t>3168731622499267568</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -8063,55 +7919,55 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>12:40:57.415</t>
+          <t>09:03:58.770</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>@el_marce</t>
+          <t>@dani_ar</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Marcelo Ríos</t>
+          <t>Daniela Arias</t>
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>7300000000002</v>
+        <v>7300000000004</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Corazón</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="H13" s="7" t="n">
-        <v>5509</v>
+        <v>5827</v>
       </c>
       <c r="I13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="7" t="n">
-        <v>10</v>
-      </c>
       <c r="K13" s="7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="M13" s="9" t="inlineStr">
         <is>
-          <t>1485711878760514322</t>
+          <t>3130715061721990327</t>
         </is>
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -8149,7 +8005,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>@ejemplo_demo</t>
+          <t>@demo_simulado</t>
         </is>
       </c>
     </row>
@@ -8161,7 +8017,7 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>7300000000000000001</t>
+          <t>7312345678901234567</t>
         </is>
       </c>
     </row>
@@ -8173,7 +8029,7 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>20260924_124018</t>
+          <t>20261014_090332</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8041,7 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>2026-09-24 12:40:18</t>
+          <t>2026-10-14 09:03:32</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8053,7 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>2026-09-24 12:40:58</t>
+          <t>2026-10-14 09:04:06</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8065,7 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>00:00:40</t>
+          <t>00:00:34</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8096,7 @@
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>89.8</v>
+        <v>104.1</v>
       </c>
     </row>
     <row r="12">
@@ -8261,7 +8117,7 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>2026-09-24 12:40:58</t>
+          <t>2026-10-14 09:04:07</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8129,7 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>C:\Users\HP\Downloads\TIKTOK DEEP\sesiones\comentarios_ejemplo_demo_20260924_124018.csv</t>
+          <t>C:\Users\HP\Downloads\TIKTOK DEEP\sesiones\comentarios_demo_simulado_20261014_090332.csv</t>
         </is>
       </c>
     </row>
@@ -8309,17 +8165,17 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>@topgifter99</t>
+          <t>@jorge_mx</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>@ana_tt</t>
+          <t>@lucia.live</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -8329,51 +8185,51 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>@jorge_mx</t>
+          <t>@mod_sofia</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>@lucia.live</t>
+          <t>@dani_ar</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>@dani_ar</t>
+          <t>@topgifter99</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>@el_marce</t>
+          <t>@ana_tt</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>@mod_sofia</t>
+          <t>@el_marce</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
